--- a/evac_by_zip/evac_by_zip_2026-09-10.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-09-10.xlsx
@@ -706,7 +706,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -714,14 +714,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
-        <v>4</v>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -730,19 +732,19 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -756,10 +758,10 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -768,86 +770,82 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
+          <t>Austin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>231</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
           <t>Grasshopper</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="E9" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
@@ -856,14 +854,16 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>225</v>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -880,26 +880,26 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>99362</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Baker, Grant</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
@@ -964,38 +964,38 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
@@ -1004,11 +1004,11 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1042,11 +1042,11 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1084,13 +1084,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>637</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>809</v>
@@ -1593,22 +1593,22 @@
     <row r="14">
       <c r="A14" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
+          <t>NF 27</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -1618,32 +1618,32 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G14" s="21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1246</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G15" s="21" t="n">
@@ -1663,22 +1663,22 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1347-C</t>
+          <t>NF 27</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G16" s="21" t="n">
@@ -1698,22 +1698,22 @@
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97358</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1247</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G17" s="21" t="n">
@@ -1733,22 +1733,22 @@
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-N</t>
+          <t>Elk Mountain</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="G18" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>97877</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-L</t>
+          <t>Mill Creek Buttes</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>Baker, Grant</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G19" s="23" t="n">
@@ -1801,269 +1801,269 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>3</v>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="n">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur South</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Gibson Prairie</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1247</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>1</v>
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406043-C</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>97358</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="n">
-        <v>1</v>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E26" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>4</v>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Mill Creek Buttes</t>
+          <t>US-OR-UMA-UMC-1406017-A</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -2073,162 +2073,162 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G27" s="23" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>Cooper Spur North</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="G28" s="25" t="n">
-        <v>158</v>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406053-C</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>Cooper Spur South</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-E</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G29" s="25" t="n">
-        <v>63</v>
+      <c r="G29" s="23" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="inlineStr">
-        <is>
-          <t>Gibson Prairie</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>4</v>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-153</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>1</v>
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>99362</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
+          <t>US-OR-UMA-UMC-1406015G</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -2256,84 +2256,84 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406015-C</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>58</v>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406053-B</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>22</v>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97877</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-GRA-GRN-043-L</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Baker, Grant</t>
         </is>
       </c>
       <c r="E35" s="23" t="inlineStr">
@@ -2353,197 +2353,197 @@
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G35" s="23" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-043-N</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G36" s="23" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015-E</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>11</v>
+      <c r="G37" s="25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-153</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="n">
-        <v>6</v>
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1246</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>5</v>
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1347-C</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406015G</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="n">
-        <v>4</v>
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1247</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>97810</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
@@ -2563,92 +2563,92 @@
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G41" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="n">
-        <v>1</v>
+      <c r="E42" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="n">
-        <v>1</v>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B44" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-039</t>
+          <t>US-OR-UNI-UCO-1435</t>
         </is>
       </c>
       <c r="C44" s="26" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D44" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E44" s="25" t="inlineStr">
@@ -2668,22 +2668,22 @@
       </c>
       <c r="F44" s="25" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="G44" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-032</t>
+          <t>US-OR-UNI-UCO-1450</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D45" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E45" s="25" t="inlineStr">
@@ -2703,22 +2703,22 @@
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G45" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1435</t>
+          <t>US-OR-BAK-BAB-1247</t>
         </is>
       </c>
       <c r="C46" s="26" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D46" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E46" s="25" t="inlineStr">
@@ -2738,22 +2738,22 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G46" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>97814</t>
         </is>
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1450</t>
+          <t>US-OR-BAK-BAB-1246</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D47" s="26" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="E47" s="25" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G47" s="25" t="n">
